--- a/DocDesign/RandomTool/Game.36/excel/MahjongSlotBetGrade.xlsx
+++ b/DocDesign/RandomTool/Game.36/excel/MahjongSlotBetGrade.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\juwawa\RandomTool\Game.36\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="MahjongSlotBetGrade" sheetId="1" r:id="rId1"/>
@@ -60,7 +65,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,12 +87,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFB5CEA8"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -579,137 +578,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -718,9 +717,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1105,7 +1101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="13.1333333333333" customWidth="1"/>
@@ -1157,7 +1153,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1165,7 +1161,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="4">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1173,7 +1169,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="4">
-        <v>20000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1181,11 +1177,24 @@
         <v>4</v>
       </c>
       <c r="B9" s="4">
-        <v>200000</v>
+        <v>10000</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:2">
-      <c r="B10" s="5"/>
+    <row r="10" spans="1:2">
+      <c r="A10" s="3">
+        <v>5</v>
+      </c>
+      <c r="B10" s="4">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="3">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4">
+        <v>100000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
